--- a/results/reliability_eval/Llama-3-8B_P1412_sample_30_tokens_0.1_temp_direct_query_scores_08-24-4.xlsx
+++ b/results/reliability_eval/Llama-3-8B_P1412_sample_30_tokens_0.1_temp_direct_query_scores_08-24-4.xlsx
@@ -477,31 +477,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.4042455006922012</v>
+        <v>0.3760267207319609</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1683658510246846</v>
+        <v>0.06463000137699043</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4042455006922012</v>
+        <v>0.3760267207319609</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1683658510246846</v>
+        <v>0.06463000137699043</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5840724187848866</v>
+        <v>0.6347473487211479</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3249611152492757</v>
+        <v>0.1047852954221967</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9844460177886226</v>
+        <v>0.9903566229985443</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9345908323881528</v>
+        <v>0.8882234432234433</v>
       </c>
       <c r="I2" t="n">
-        <v>0.197</v>
+        <v>0.08400000000000001</v>
       </c>
     </row>
   </sheetData>
